--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486360_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486360_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5418</v>
+        <v>8.166</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0778</v>
+        <v>6.3013</v>
       </c>
       <c r="F2" t="n">
-        <v>1.464</v>
+        <v>1.8648</v>
       </c>
       <c r="G2" t="n">
         <v>9.4237</v>
@@ -610,13 +610,13 @@
         <v>2.6101</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1869</v>
+        <v>-0.5627</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.2151</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1785</v>
+        <v>-0.7778</v>
       </c>
       <c r="V2" t="n">
         <v>-1.13</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. BROWN-FERGUSON</t>
+          <t>J. ZIDEK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7218</v>
+        <v>6.0681</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6887</v>
+        <v>2.0776</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0332</v>
+        <v>3.9905</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2442</v>
+        <v>5.8072</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4123</v>
+        <v>0.7846</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8319</v>
+        <v>5.0226</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0929</v>
+        <v>4.0224</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9016</v>
+        <v>0.7879</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1912</v>
+        <v>3.2345</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1513</v>
+        <v>1.7848</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5107</v>
+        <v>-0.0033</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6407</v>
+        <v>1.7881</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7174</v>
+        <v>-0.2818</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0769</v>
+        <v>-0.5299</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7943</v>
+        <v>0.2481</v>
       </c>
       <c r="V3" t="n">
         <v>0.7602</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. ZIDEK</t>
+          <t>J. BROWN-FERGUSON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.6596</v>
+        <v>4.8818</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8541</v>
+        <v>2.4651</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8056</v>
+        <v>2.4167</v>
       </c>
       <c r="G4" t="n">
-        <v>5.8072</v>
+        <v>4.2442</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7846</v>
+        <v>3.4123</v>
       </c>
       <c r="I4" t="n">
-        <v>5.0226</v>
+        <v>0.8319</v>
       </c>
       <c r="J4" t="n">
-        <v>4.0224</v>
+        <v>3.0929</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7879</v>
+        <v>2.9016</v>
       </c>
       <c r="L4" t="n">
-        <v>3.2345</v>
+        <v>0.1912</v>
       </c>
       <c r="M4" t="n">
-        <v>1.7848</v>
+        <v>1.1513</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0033</v>
+        <v>0.5107</v>
       </c>
       <c r="O4" t="n">
-        <v>1.7881</v>
+        <v>0.6407</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9576</v>
+        <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6903</v>
+        <v>-0.1226</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.3004</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.1778</v>
       </c>
       <c r="V4" t="n">
         <v>0.7602</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.292</v>
+        <v>4.0068</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5978</v>
+        <v>0.3743</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6942</v>
+        <v>3.6325</v>
       </c>
       <c r="G5" t="n">
         <v>3.1516</v>
@@ -844,13 +844,13 @@
         <v>1.9576</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0104</v>
+        <v>0.7252</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8051</v>
+        <v>0.5816</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2052</v>
+        <v>0.1436</v>
       </c>
       <c r="V5" t="n">
         <v>0.5649999999999999</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.1467</v>
+        <v>3.8152</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6493</v>
+        <v>0.9788</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4974</v>
+        <v>2.8365</v>
       </c>
       <c r="G6" t="n">
         <v>0.5268</v>
@@ -922,13 +922,13 @@
         <v>2.3926</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8581</v>
+        <v>0.5266</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7557</v>
+        <v>1.0851</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8976</v>
+        <v>-0.5585</v>
       </c>
       <c r="V6" t="n">
         <v>1.6743</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.3323</v>
+        <v>3.0241</v>
       </c>
       <c r="E7" t="n">
         <v>2.1962</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1362</v>
+        <v>0.828</v>
       </c>
       <c r="G7" t="n">
         <v>4.1683</v>
@@ -1000,13 +1000,13 @@
         <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>0.536</v>
+        <v>0.2277</v>
       </c>
       <c r="T7" t="n">
         <v>0.9421</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4062</v>
+        <v>-0.7144</v>
       </c>
       <c r="V7" t="n">
         <v>0.5857</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1888</v>
+        <v>2.7361</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0246</v>
+        <v>-0.3541</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2135</v>
+        <v>3.0902</v>
       </c>
       <c r="G8" t="n">
         <v>2.7009</v>
@@ -1078,13 +1078,13 @@
         <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5773</v>
+        <v>-0.03</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.548</v>
+        <v>0.1226</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0293</v>
+        <v>-0.1526</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3698</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2787</v>
+        <v>1.5909</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7349</v>
+        <v>1.2936</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5438</v>
+        <v>0.2972</v>
       </c>
       <c r="G9" t="n">
         <v>0.8436</v>
@@ -1156,13 +1156,13 @@
         <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.08749999999999999</v>
+        <v>0.2247</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1286</v>
+        <v>0.6874</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2161</v>
+        <v>-0.4627</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5649999999999999</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1501</v>
+        <v>0.135</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1498</v>
+        <v>-0.9263</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9997</v>
+        <v>1.0613</v>
       </c>
       <c r="G10" t="n">
         <v>0.1568</v>
@@ -1234,13 +1234,13 @@
         <v>0.435</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3939</v>
+        <v>-0.1088</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.137</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2569</v>
+        <v>-0.1953</v>
       </c>
       <c r="V10" t="n">
         <v>0.7395</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. HUELVES GARCIA</t>
+          <t>G. GIL GARCIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9604</v>
+        <v>-2.049</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3744</v>
+        <v>-2.8983</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.586</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9748</v>
+        <v>0.6669</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5078</v>
+        <v>-1.6544</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.467</v>
+        <v>2.3212</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.248</v>
+        <v>-0.1753</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2679</v>
+        <v>-1.3044</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0199</v>
+        <v>1.1292</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2732</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7601</v>
+        <v>-0.3499</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4869</v>
+        <v>1.1921</v>
       </c>
       <c r="P11" t="n">
-        <v>1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R11" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1645</v>
+        <v>-0.4984</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8736</v>
+        <v>-0.548</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7091</v>
+        <v>0.0496</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4552</v>
+        <v>-1.13</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4552</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. GIL GARCIA</t>
+          <t>A. HUELVES GARCIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1415</v>
+        <v>-2.4653</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8983</v>
+        <v>-1.1567</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7568</v>
+        <v>-1.3086</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6669</v>
+        <v>-0.9748</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6544</v>
+        <v>-0.5078</v>
       </c>
       <c r="I12" t="n">
-        <v>2.3212</v>
+        <v>-0.467</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1753</v>
+        <v>-1.248</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.3044</v>
+        <v>-1.2679</v>
       </c>
       <c r="L12" t="n">
-        <v>1.1292</v>
+        <v>0.0199</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.2732</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3499</v>
+        <v>0.7601</v>
       </c>
       <c r="O12" t="n">
-        <v>1.1921</v>
+        <v>-0.4869</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5909</v>
+        <v>-0.3404</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.548</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0429</v>
+        <v>-0.4317</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.13</v>
+        <v>-2.4552</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.13</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>29.90969999999999</v>
+        <v>29.9097</v>
       </c>
       <c r="E13" t="n">
-        <v>10.3517</v>
+        <v>10.3515</v>
       </c>
       <c r="F13" t="n">
         <v>19.5584</v>
@@ -1435,7 +1435,7 @@
         <v>30.7152</v>
       </c>
       <c r="H13" t="n">
-        <v>7.5423</v>
+        <v>7.542299999999999</v>
       </c>
       <c r="I13" t="n">
         <v>23.1727</v>
@@ -1450,7 +1450,7 @@
         <v>20.1686</v>
       </c>
       <c r="M13" t="n">
-        <v>9.023100000000001</v>
+        <v>9.023099999999999</v>
       </c>
       <c r="N13" t="n">
         <v>6.019299999999999</v>
@@ -1468,10 +1468,10 @@
         <v>17.4005</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2404000000000002</v>
+        <v>-0.2405000000000002</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4333</v>
+        <v>2.4334</v>
       </c>
       <c r="U13" t="n">
         <v>-2.6739</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5862</v>
+        <v>2.7481</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3211</v>
+        <v>0.5446</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2651</v>
+        <v>2.2034</v>
       </c>
       <c r="G14" t="n">
         <v>1.9368</v>
@@ -1546,13 +1546,13 @@
         <v>1.9576</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5686</v>
+        <v>-0.4068</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6165</v>
+        <v>-0.3929</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0478</v>
+        <v>-0.0138</v>
       </c>
       <c r="V14" t="n">
         <v>-0.7395</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. CHAPELA LAGE</t>
+          <t>A. URDIAIN LABAYEN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3226</v>
+        <v>2.0511</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6841</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0067</v>
+        <v>1.2945</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0402</v>
+        <v>-1.3066</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4688</v>
+        <v>0.0911</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5714</v>
+        <v>-1.3977</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4499</v>
+        <v>-0.2824</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2227</v>
+        <v>0.4594</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2272</v>
+        <v>-0.7418</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4097</v>
+        <v>-1.0241</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2461</v>
+        <v>-0.3683</v>
       </c>
       <c r="O15" t="n">
         <v>-0.6558</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>1.0875</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
         <v>2.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7177</v>
+        <v>-0.3596</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9589</v>
+        <v>-0.1334</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2413</v>
+        <v>-0.2262</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2.6297</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. URDIAIN LABAYEN</t>
+          <t>A. CHAPELA LAGE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7563</v>
+        <v>1.9315</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1375</v>
+        <v>-0.0136</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8938</v>
+        <v>1.945</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.3066</v>
+        <v>2.0402</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0911</v>
+        <v>1.4688</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.3977</v>
+        <v>0.5714</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2824</v>
+        <v>2.4499</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4594</v>
+        <v>1.2227</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7418</v>
+        <v>1.2272</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0241</v>
+        <v>-0.4097</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3683</v>
+        <v>0.2461</v>
       </c>
       <c r="O16" t="n">
         <v>-0.6558</v>
       </c>
       <c r="P16" t="n">
-        <v>1.0875</v>
+        <v>-0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R16" t="n">
         <v>2.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.6544</v>
+        <v>-0.1088</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0274</v>
+        <v>-0.2884</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6269</v>
+        <v>0.1796</v>
       </c>
       <c r="V16" t="n">
-        <v>2.6297</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0351</v>
+        <v>0.2355</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0248</v>
+        <v>-0.5778</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0599</v>
+        <v>0.8133</v>
       </c>
       <c r="G17" t="n">
         <v>-0.9618</v>
@@ -1780,13 +1780,13 @@
         <v>2.8276</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0171</v>
+        <v>0.2175</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1454</v>
+        <v>0.3016</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1625</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="V17" t="n">
         <v>-0.7602</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8394</v>
+        <v>-0.8086</v>
       </c>
       <c r="E18" t="n">
         <v>-0.8455</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0061</v>
+        <v>0.0369</v>
       </c>
       <c r="G18" t="n">
         <v>-1.009</v>
@@ -1858,13 +1858,13 @@
         <v>0.435</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2655</v>
+        <v>-0.2346</v>
       </c>
       <c r="T18" t="n">
         <v>-0.137</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. CARRALERO MARTIN</t>
+          <t>N. CAMACHO DE SÁ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7146</v>
+        <v>-2.6847</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2082</v>
+        <v>0.2492</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5064</v>
+        <v>-2.9339</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.5339</v>
+        <v>-5.8696</v>
       </c>
       <c r="H19" t="n">
-        <v>0.228</v>
+        <v>-0.9856</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.7619</v>
+        <v>-4.884</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2983</v>
+        <v>-1.9544</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0434</v>
+        <v>-0.6173</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7451</v>
+        <v>-1.3371</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.8322</v>
+        <v>-3.9151</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8153</v>
+        <v>-0.3683</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.0169</v>
+        <v>-3.5468</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3926</v>
+        <v>1.5225</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8193</v>
+        <v>0.5324</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5608</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2585</v>
+        <v>-0.3461</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.13</v>
+        <v>1.13</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1952</v>
+        <v>1.3252</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3252</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. CAMACHO DE SÁ</t>
+          <t>J. CARRALERO MARTIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8022</v>
+        <v>-3.4719</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2551</v>
+        <v>-1.9963</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.0572</v>
+        <v>-1.4755</v>
       </c>
       <c r="G20" t="n">
-        <v>-5.8696</v>
+        <v>-2.5339</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9856</v>
+        <v>0.228</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.884</v>
+        <v>-2.7619</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.9544</v>
+        <v>0.2983</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6173</v>
+        <v>1.0434</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3371</v>
+        <v>-0.7451</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.9151</v>
+        <v>-2.8322</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3683</v>
+        <v>-0.8153</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.5468</v>
+        <v>-2.0169</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5225</v>
+        <v>-0.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5225</v>
+        <v>2.3926</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4149</v>
+        <v>1.062</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8843</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4694</v>
+        <v>0.2893</v>
       </c>
       <c r="V20" t="n">
-        <v>1.13</v>
+        <v>-1.13</v>
       </c>
       <c r="W20" t="n">
-        <v>1.3252</v>
+        <v>0.1952</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1952</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="21">
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6944</v>
+        <v>-4.2532</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3251</v>
+        <v>-1.8839</v>
       </c>
       <c r="F21" t="n">
         <v>-2.3693</v>
@@ -2092,10 +2092,10 @@
         <v>0.2175</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4711</v>
+        <v>-0.0877</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8736</v>
+        <v>0.3149</v>
       </c>
       <c r="U21" t="n">
         <v>-0.4026</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.117100000000001</v>
+        <v>-6.7953</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.637</v>
+        <v>-3.4076</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.4801</v>
+        <v>-3.3876</v>
       </c>
       <c r="G22" t="n">
         <v>-8.2827</v>
@@ -2170,13 +2170,13 @@
         <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7469</v>
+        <v>-0.4251</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9589</v>
+        <v>0.2704</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.788</v>
+        <v>-0.6955</v>
       </c>
       <c r="V22" t="n">
         <v>1.695</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.1799</v>
+        <v>-7.0314</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.8761</v>
+        <v>-3.7586</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.3037</v>
+        <v>-3.2729</v>
       </c>
       <c r="G23" t="n">
         <v>-4.6518</v>
@@ -2248,13 +2248,13 @@
         <v>1.305</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5705</v>
+        <v>-0.4221</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8904</v>
+        <v>0.2271</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.68</v>
+        <v>-0.6492</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.2624</v>
+        <v>-11.8308</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.3961</v>
+        <v>-8.625500000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.8663</v>
+        <v>-3.2053</v>
       </c>
       <c r="G24" t="n">
         <v>-6.2589</v>
@@ -2326,13 +2326,13 @@
         <v>1.0875</v>
       </c>
       <c r="S24" t="n">
-        <v>2.0416</v>
+        <v>0.4732</v>
       </c>
       <c r="T24" t="n">
-        <v>2.0898</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0482</v>
+        <v>-0.3873</v>
       </c>
       <c r="V24" t="n">
         <v>-1.695</v>
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-29.9098</v>
+        <v>-29.9097</v>
       </c>
       <c r="E25" t="n">
-        <v>-19.5582</v>
+        <v>-19.5584</v>
       </c>
       <c r="F25" t="n">
         <v>-10.3514</v>
@@ -2404,10 +2404,10 @@
         <v>17.4005</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2403999999999995</v>
+        <v>0.2404000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>2.674</v>
+        <v>2.6739</v>
       </c>
       <c r="U25" t="n">
         <v>-2.4335</v>
